--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.54745241819148</v>
+        <v>4.151461017956115</v>
       </c>
       <c r="D2" t="n">
-        <v>25.50681722912234</v>
+        <v>4.144857799732381</v>
       </c>
       <c r="E2" t="n">
-        <v>5.539684533040701</v>
+        <v>0.900198736619114</v>
       </c>
       <c r="F2" t="n">
-        <v>5.511194820838516</v>
+        <v>0.8955691583862587</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.11454778992852</v>
+        <v>2.781114015863384</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17374778116075</v>
+        <v>2.790734014438622</v>
       </c>
       <c r="E3" t="n">
-        <v>5.539684533040701</v>
+        <v>0.900198736619114</v>
       </c>
       <c r="F3" t="n">
-        <v>5.511194820838516</v>
+        <v>0.8955691583862587</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.89417488372651</v>
+        <v>3.395303418605558</v>
       </c>
       <c r="D4" t="n">
-        <v>21.00113207008871</v>
+        <v>3.412683961389416</v>
       </c>
       <c r="E4" t="n">
-        <v>5.539684533040701</v>
+        <v>0.900198736619114</v>
       </c>
       <c r="F4" t="n">
-        <v>5.511194820838516</v>
+        <v>0.8955691583862587</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.95994615483049</v>
+        <v>5.193491250159955</v>
       </c>
       <c r="D5" t="n">
-        <v>31.9787512102798</v>
+        <v>5.196547071670468</v>
       </c>
       <c r="E5" t="n">
-        <v>5.539684533040701</v>
+        <v>0.900198736619114</v>
       </c>
       <c r="F5" t="n">
-        <v>5.511194820838516</v>
+        <v>0.8955691583862587</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
